--- a/excel/distribuidora-aurelio-s-a-c_ruta_proxima_semana.xlsx
+++ b/excel/distribuidora-aurelio-s-a-c_ruta_proxima_semana.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rutas'!$A$1:$J$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,19 +428,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,8 +495,7548 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C004039410</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>48491247</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GOYAS MATTA NADIA VANESSA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AA.HH. KEIKO SOFIA Mz I, Lote 02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C004016314</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>47107251</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SANEZ CULLANCO YENNY ROSMERY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>AA.HH Keiko Sofia Mz D Lt 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C001644114</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44878626</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FABIAN BORJA MIRIAM CAROLINA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>AAHH KEIKO SOFIA MZA. Ñ LOTE. 1 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C001724154</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80048351</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MAGALLANES QUIROZ VICTOR ALBERTO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>KEIKO SOFIA MZA. S LOTE. 12 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C001519010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41868206</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PAUCAR LAZARO LUZMIA MARIELA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UPIS KEIKO SOFIA MZA. W LOTE. 8 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C004252684</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70337859</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GARCIA ÑAHUI ERIKA JANET</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AA.HH. Keiko Sofia Mz 3 Lote 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C004013343</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23557323</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MARTINEZ COLQUEPISCO MARIA SUSANA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AA.HH. EL SALVADOR Mz N, Lte 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C001488964</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43912285</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CHICO AVALOS DE MARTINEZ PATRICIA MARIVE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PN2 / AV. FE Y ALEGRIA LOTE. 16 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C004202566</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42580701</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HUINCHO APOLINARIO DIANA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AA.HH. Los Ángeles Mz D Lote 4 Leon de Vivero</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C001744169</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21814052</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MAGALLANES RAMOS ROSA MARIA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>LEON DE VIVERO MZA. 6 LOTE. 22 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C001029858</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21872732</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PALOMINO DE GUERRERO MARIA MARLENE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>URB LEON DE VIVERO 21 MZA. B1 LOTE. 21 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C004240700</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21522345</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CASTILLO GUEVARA ANALY</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Urb. Leon de Vivero Mz 14 Lt 07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C004060574</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21879563</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>GALVEZ HUAMANI FRANCISCO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AA.HH EL SALVADOR Mz 5 Lote 12 PUEBLO NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C004186527</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>77906278</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>HUAYCOCHEA AGUILAR KRISTEL MIRIAM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>AV. UNION Nº 157</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C000957605</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10218577755</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CASTILLO MAGALLANES DORA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>URB LEON DE VIVERO NRO. 21 MZA. B1 LOTE. 21 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C001007435</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21872510</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FIGUEROA GENTILLE DOMINGA BEATRIZ</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MERCADO SAN ISIDRO PSTO. 102 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C001710990</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43025729</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CASTILLON ROMERO MARIELA JENNY</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>URB LOS VIÑEDOS MZA. A LOTE. 22 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C004205768</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46135866</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OJANAMA RIOS MARVELITH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>JR. FRANCISCO BOLOGNESI MZ 13 LT 11A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C004238943</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8994148</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ESPINOZA ROMERO MYRIAM HERMINIA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Grocio Prado (Chincha)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Los Viñedos Mz 1 Lote 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C001130629</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>21872938</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>YATACO YATACO MARIA ANGELICA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AV. PRIMAVERA 455 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C000962211</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>80046034</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ARIAS SOSA VILMA MARIBEL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MERCADO PUEBLO NUEVO NRO. 24 PSTO. 181 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C001504555</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21829253</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VILCAPUMA QUINCHO MARTHA BELINDA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>MERCADO PUEBLO NUEVO Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C001287594</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>40976047</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CHUQUISPUMA CHIPANA ASCENCIONA ROSALINA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>MERCADO PUEBLO NUEVO INT. 55 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C001196568</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>21872692</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>YALLE RONDON CARMEN ELENA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MERCADO PUEBLO NUEVO PSTO. 4 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C004063309</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>74949411</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>CARDENAS MUNAYCO ARMANDO TEODORO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Grocio Prado (Chincha)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Av. Mariscal Benavides 1141</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C001542655</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>21880847</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HUAMAN RAMOS MARIA ESTELA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>PROLONG ARICA Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C001724311</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48637847</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>PACCORE ÑAÑEZ SANDRA ISAURA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CALLE SUCRE 672 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C001531107</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21829482</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>CARCAMO DE BELLIDO DOMENICA</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MCDO. FERIAL Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C001160765</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>45597799</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DIAZ FLORES JUDITH MONICA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SANTOS NAGARO Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C001421816</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10218341123</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>TASAYCO MARTINEZ JUANA YSABEL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AV. OSCAR R BENAVIDES-CDRA 4 INT. 466 URB. MERCADO DE ABASTOS Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C001539865</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>10218296616</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>TASAYCO CARBAJAL GLORIA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>CL. SUCRE NRO. 328 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C004064580</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>21804585</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>GONZALES GONZALES YSABEL APOLONIA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Calle Sucre s/n</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C004240068</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>73083681</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>TORRES PEÑA MARIA MILAGROS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Av. Jose Faustino Sanchez Carrión Pto.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C000962567</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>44407216</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CABANILLAS ELEFONIO MARIA ESTRELLA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PARADA MUNICIPAL MZA. 19 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C001718496</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>21882002</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ALCA HERRERA ANGELA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>JR. SANTO DOMINGO Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C000960787</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10410923764</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LARENAS CASTILLA GUSTAVO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AV. MER MODELO P250 MZA. MAZAA370 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C001556310</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>43023491</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>MUNAYCO VASQUEZ HAYDEE YANINA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MERCADO MODELO Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C004014001</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>20996625</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MARTINEZ VARILLAS PATRICIA LILIANA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MERCADO MODELO PUESTO 170 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C001714400</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>47979929</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>BONIFACIO CHAVEZ JAHAIRA ROSITA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CALLE JUNIN NRO. 501 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C004251085</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>75187086</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>VARGAS MORENO CAMILA DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Calle Junin 550 - Frente al Seguro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C000959392</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10218245809</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CHING BENAVIDES RAUL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>JR. CAL MIGUEL GRAU N193 NRO. 193 MZA. MAZAA010 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C001695040</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>10218873320</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>MORA AVALOS MARGARITA YOLANDA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CL. ACEQUIA GRANDE NRO. 901 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C000956528</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>21808684</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>CABRERA CARBAJAL ROSA ELENA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>AV. GARCILAZO DE LA VEGA 470 MZA. MANZANA030 Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C004248822</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>21868063</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>PACHAS PACHAS NOELIA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Calle Ricardo Palma 189 Acequia Grande</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C001368585</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>21849038</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>LEVANO AVALOS GLADYS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AV. MINA DE ORO NRO. 820 Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C001716210</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>42385462</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HERNANDEZ MEJIA DE ARCE ROSA ELENA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA NRO. 132 URB. SEGUNDA ETAPA Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C001742989</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>73957573</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>RAMIREZ TORRES MARTIN ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CL. CALLE NUEVA MZA. B LOTE. 16 URB. ANTES HOSPEDAJE LOS PINOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C001707226</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>21872723</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HERRERA ERRIBARI LEONOR</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>AV UNION 179 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C004221528</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>76033971</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ANTON ONCEVAY ERICKA EDUARDA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Av. San Martin 501</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C001555985</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>43796700</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SEBASTIAN MORAN TANIA ZABRINA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>AV. MIRAFLORES 127 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C004023217</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>77815250</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VELA PISCO MAGNO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AV. PROGRESO 175 ICA-CHINCHA-CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>C001675821</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>21878498</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CCAPA CRUZ DE PACHAS SANDRA MARIBEL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>AV GROCIO PRADO 140 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>C004060584</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>21804090</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SEBASTIAN CABALLERO JUANA NELLY</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>AV. GERARDO SOTELO Lote 10 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>C001548406</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>21879015</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>MOSCAYZA ARTEAGA FANNY</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AV. GERARDO SOTELO MZA. T LOTE. 9 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C004014312</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>41331524</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>QUINTANA ISUIZA KELLY GERALDINE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Alva Maurtua Mz A Lt 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>C004051480</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>43949735</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>BONIFACIO DIAZ VENTURA MARIBEL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>AV. SAN MARTIN 136 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>C001216599</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>21794628</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>GRATTA DE ARBURUA ANGELITA MERCEDES</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AV. ALVA MAURTUA NRO. 680 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>C001006107</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>21815165</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>LEVANO MARCOS ANA MARIA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>AV. LA FLORIDA  COSTADO HOSPITAL SAN JOSE Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>C000960181</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>21790943</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SALAZAR GONZALES MARITZA ELENA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>AV. FLORIDA 310 MANZANA 390 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>C001659080</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10420645797</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>APOLAYA MARCOS DIANA EVELYN</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>CL. LUIS ALVA MAURTUA NRO. 317 INT. 2 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C001689928</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>21876225</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DEL RIO MENDOZA ROSA ZENOVIA</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>AV. SAN MARTIN TUPAC ZONA A 341 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C001511661</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>21865305</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>TENORIO PARIONA DE PUMA SANDY GRACIELA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN MZA. U LOTE. 28 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C001666047</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>75490737</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ENRIQUE HUAMAN CINTHIA MARIA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN LOTE. 16 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C004183669</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>23270717</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>QUISPE CHANCHA JORGE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Upis San Agustín Mz 1 Lote 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C004065709</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>60887139</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ CLEMENTE LEONEL EDMILSON</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN Mz V Lote 01 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C004189117</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>41374467</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ORMEÑO PEÑALOZA SANDY LISSET</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>AA.HH Villa Sol Mz F Lote 13 José Olaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C004049432</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>44263184</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>VILLOSLADA CERAZO DAYSI DIANA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>AV. SANTA ROSA Mz K Lote 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C004097166</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>7070448</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PALOMINO OBIAGA ESTHER</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>JR. CUZCO Mz E Lote 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>C001086594</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>21844364</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>RAMOS CAHUANA SONIA ISABEL</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AAHH MICAELA BASTIDA MZA. E LOTE. 7 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C004185405</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>62723782</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MARTINEZ MACHUCA KENIA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AA.HH MICAELA BASTIDAS MZ G LT 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>C001733929</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>48164409</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SALVATIERRA MOTTA YAMELI MILAGROS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>URB. OLIVA RAZZETO 1 MZA. D LOTE. 06 Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C001433290</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>10409754282</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>BELLEZA CARPIO ANGELA ELIZABETH</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Pueblo Nuevo (Chincha)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>MZA. C LOTE. 02 URB. URB OLIVA RAZZETO Ica-Chincha-Pueblo Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C001130302</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>10218131315</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>RONCEROS FIGUEROA CARLOS ALBERTO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CL. SAN JOSE NRO. 198 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C001216596</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>23524279</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>DEL RIO DE SALVATIERRA LUZMILA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>AV. ANDRES AVELINO CACERES 148 POR EL COLISEO - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>C004048135</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>62021171</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>PADILLA PINO ALYSON LORENA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PASAJE GARAY 198 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C001495873</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>21782651</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CHACALIAZA VELIZ EDITH PIEDAD</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PASAJE OLAYA NRO. 620 INT. 6 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C000961864</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>21863612</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>HUAMAN AVALOS ELIZABETH ROSARIO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>AV. LUIS MASSARO 793 MZA. MANZANA034  Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C001565925</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>10760415591</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PASACHE CHACALIAZA CAROLIN DEYANIRA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>AV. PILPA NRO. 811 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C001687429</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>41223811</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>TASAYCO DE LA CRUZ SARA MARIANELLA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>AV. LUIS MASSARO 819 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C000959225</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>21868561</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ORTIZ MARCOS DE PACHAS MARIA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>AV. VICTORIA 311 POR COLEGIO COOPERATIVO Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>C004036014</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>21812546</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>QUISPE GUERRA MARIA DEL PILAR</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>AV. VICTORIA 265 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C004039631</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>21874798</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LOZANO CARBAJAL VDA DE MEDINA GLORIA NIL</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>AV. PILPA 751</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>C000956193</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>10218014122</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>VELIZ VALENZUELA SARELA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>AV. AVE BOM BOM CORONADO N787 NRO. 787 MZA. MAZAA18C URB. CHINCHA ALTA Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>C004183666</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>21815460</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CRISOSTOMO FELIX GLORIA LILY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Pasaje Marcela 807-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>C004183464</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>43145532</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>JIMENEZ PAUCAR DIANA CAROLINA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Mercado Cruz Blanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>C001512442</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>42981783</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>NAPA MARTINEZ ESMERALDA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>AV. JOSE OLAYA 139 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C004242592</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>75340693</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>HUAMAN VASQUEZ LUIGUI KENY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Av. Jose Olaya 208 Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C004042214</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>70447588</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>RAMOS MARTINEZ CAROLINA XIMENA</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PASAJE RIVAS 145 - 4 ICA-CHINCHA-CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C001738166</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>75480015</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>LOBATON MARCELO MARIA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PLZ. PROLONG SANTO DOMINGO NRO. 621 INT. 6 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C001552713</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>21808446</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>CESPEDES ALMEYDA MARIA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>CALLE SANTO DOMINGO 621 INT. 7 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C001738817</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>45912779</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>MAGALLANES ALVAREZ SCHEYLA ELOISA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>CALLE COLON 594 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C004238718</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>21880895</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>PAREJA CAMPOS CARMEN MAGALY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Jr. Colon 593</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C004176969</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>48310476</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>HUARIPAUCAR LIFONZO MARIA LUISA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PROLONG. ALVA MAURTUA 190</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>C001375507</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>10217996517</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>GONZALES HUAMANI LEONOR AURELIA</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>CL. CHAVALINA NRO. 130 INT. 01 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C001370888</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>21863400</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MENESES MAGALLANES JOVANA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PROLONG COLON 785 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C001403118</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>41680405</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>TAPIA YAMOCA ROSA YSABEL</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>BARRIO CHAVALINA 371 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>C004049700</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>45449769</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>GUERRA CASTILLA MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>CALLE FELIPE CHICO 190 SUNAMPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C001531420</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>41465146</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>DE LA CRUZ NOVA NORALI DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PASAJE VICTORIA MZA. MK LOTE. 23 Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>C001562372</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>10458311965</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>MENDOZA LEVANO RAQUEL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>NRO. 446 URB. BARRIO SAN MARTIN Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>C001651237</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>74363339</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>TASAYCO VALDERRAMA GRISSEL IVON</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Sunampe (Chincha)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PJE. PASAJE APOLAYA NRO. 190 Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C001481621</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>76957879</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>GARCIA PASTOR JESUS ADEMIR</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>AV. SAN MARTIN MZA. 021 LOTE. 3 Ica-Chincha-Sunampe</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>C000956456</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>10217861603</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>MATEO LEVANO LEONCIO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>AV. AVE PANAMERICANA SUR KM 200 N MZA. MAZAA070 URB. CHINCHA ALTA Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C001685023</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>75863869</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>PEREZ VALENCIA ARACELI SARELA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>AV. AMERICA 546 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C004013298</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>42761946</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>PINA MONTESINOS JOSE ALBERTO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Av. América N° 619</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>C001743073</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>22307297</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>CASTILLA TORRES MIRIAM SUSANA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>AV. PROGRESO 250 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C001370354</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>21853011</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>RIOS RODRIGUEZ DE HERRERA EDELMIRA ESPER</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>CALLE SANTA RITA 100 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C004159771</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>76511869</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>PALOMINO HUAMAN NAYELI BRIGITT</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>AV. JOSE OLAYA 420</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C004208912</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>76693342</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>TIPICIANO SANDIGA CINTHIA ANDREA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>A.H. Virgen de Fátima Mz F Lote 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C001656137</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>21810967</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SOTELO DE YATACO BERTHA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>AH ROSA DE LAS AMERICAS MZ F LOTE 1 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C000957281</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>21860523</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>PACHAS SARAVIA ROSA GLADYS</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PJE. BENAVIDES 149 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>C004186535</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>60807548</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ANCHANTE PEREZ EDITH CELESTE</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>AA.HH SEÑOR DE CACHUY MZ A LT 07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>C001506135</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>21796220</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>RAMOS ATUNCAR JUAN GREGORIO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PJE. SANTA MARIA 286 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>C000957364</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>10218790726</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ALANYA CAHUANA MIRIAM</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>AV. OTR PAN SUR KM 199 N-728 NRO. 728 MZA. MANZANA39A URB. ANTES DE CHICO MUNAYCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C000956344</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>21837063</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>DEL RIO SALVATIERRA NICEFORO MAURO</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>MERCADO CRUZ BLANCA - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>C001513220</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>45554289</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>GONZALES QUISPE MADELEYNE</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>MERCADO CRUZ BLANCA - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>C001725213</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>10703125889</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>TASAYCO SANTIAGO GERALDINE</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>AV. ARENALES NRO. 610 URB. ANTES MERCADO CRUZ BLANCA Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C001725214</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>44397980</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MARTINEZ DE LA CRUZ ANITA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>MERCADO CRUZ BLANCA INT. 15 PSTO A - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>C001735361</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>44545566</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>GUERRA GUTIERREZ MARGARITA LIZET</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>MERCADO CRUZ BLANCA 123 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>C004242596</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>21861906</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>YATACO ATUNCAR ANGELICA CECILIA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>AA.HH. Virgen del Carmen Mz G Lt 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C004023219</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>21860727</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>PACHAS ALMEYDA CECILIA PAULA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PASAJE RODOLFO PACHAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C001571354</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>21869871</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>NOLAZCO HUAYTA YSABEL CRISTINA</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>AV. CENTENARIO MZA. 8 LOTE 1 - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C004033225</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>80042981</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ENRIQUEZ DE LA CRUZ CARMEN ROSA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>JR. INCA ROCA S/N CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C001748920</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>74486009</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>HERRERA QUISPE YAHAIRA LISETH</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN MZA. B1 LOTE. 24 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C000956246</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>21856545</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PEREZ MACHUCA SILVIA BELEN</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN MB1 L27 MZA. MANZANA350 LOTE. 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C001508654</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>48577684</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>CHAVEZ RONDON GABRIELA LUZ</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN MZA. Q LOTE. 6 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C001508647</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>21885050</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>HUAYLLANI TAIPE NELFA</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN MZA. K LOTE. 40 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>C004007842</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>21784294</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>CAQUIAMARCA GODOY SILVERIA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Upis San Agustin Mz. D Lt. 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C004028231</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>75765350</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ROJAS CUSI ANA MARIA</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>UPIS SAN AGUSTIN ANTES DEL COLEGIO SAN AGUSTINPIS SAN AGUSTIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>C001748703</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>21871626</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>GARCIA PAUCAR ANGELICA EDITH</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>AV. UPIS SAN AGUSTIN / SAN LUIS MZA. D LOTE. 9 Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C001730100</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>10218877601</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>VALENZUELA LLANCARI SOLEDAD ROSARELA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>MZA. P LOTE. 10 URB. UPIS SAN AGUSTIN Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>C001507939</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>21858250</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>DAVALOS MUNARRIZ ELMARIA</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>UPIS SAN LUIS INT. 7 MZA. H Ica-Chincha-Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>C004094490</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>72368070</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>GUILLEN PACHAS KARINA LISSETT</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>BARRIO EL TIGRE  391 CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>C000958704</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>40261249</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>LOPEZ LAZARO CELIA ROSALVINA</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>MERCADO CRUZ BLANCA - Chincha Alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C004183297</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>41651447</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>CENTENO ESPINOZA LUPE CHARO</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Mercado Cruz Blanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C004014506</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>21804933</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>AUQUES MARCOS DELFINA FELICITA</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Av. América N°599</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C004007849</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>21867563</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>BLAS CHAVEZ REGINA ANA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Psje. Los Pinos N° 122 ICA-CHINCHA-CHINCHA ALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C004001953</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>20612285838</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>MEYGER E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>AV. SANTOS NAGARO NRO. 148</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C004014467</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>21810998</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ALMEYDA SIFUENTES LOURDES MERCEDES</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Calle Sucre 707</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C004016283</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>RUC</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>20612506681</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>INVERSIONES Y SERVICIOS K&amp;N S.A.C.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AV. MARISCAL BENAVIDES NRO. 257</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C004009366</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>48411645</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>BAILETTI LAVERDE BRIGGITTE FRANCESCA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Av. Santos Nagaro N°142</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C001509445</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>45228039</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SEGAMA SEDANO MILKA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>URB CASA GRANDE Ica-Chincha-Alto Laran</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C004173312</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>43194734</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>CONDOR QUISPE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>SEÑOR DE LOS MILAGROS AV. LAS TUNAS MZA C1-LOTE 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>C004217853</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>45127224</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>NOLBERTO CARBAJAL MIRIAN KARINA</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>AA.HH SEÑOR DE LOS MILAGROS 6TA ETAPA MZ I2 LT 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>C004217847</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>21812587</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>FERNANDEZ AYBAR BETZABE LIBIA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>AA.HH SEÑOR DE LOS MILAGROS 6TA ETAPA MZ I2 LT 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SUSANA SOFIA FERIA QUISPE</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>C004217859</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>47583913</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ORE LLACTA ROSALINDA</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>CHINCHA</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Chincha Alta (Chincha)</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>AA.HH SEÑOR DE LOS MILAGROS 6TA ETAPA MZ D3 LT 12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>